--- a/Projects/MISQ/MISQ round 2/analysis/outputs/explore260527_selected results and plot.xlsx
+++ b/Projects/MISQ/MISQ round 2/analysis/outputs/explore260527_selected results and plot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylanchen/Desktop/geek-community/Projects/MISQ/MISQ round 2/analysis/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3530104-7465-A042-AAF9-AF8A3BEDD6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80748DA6-6580-5A43-BE70-3E9C171098EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="38200" windowHeight="19260" activeTab="1" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="38160" windowHeight="19180" activeTab="1" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="324">
   <si>
     <t>DV: # human answers</t>
   </si>
@@ -1067,6 +1067,9 @@
   </si>
   <si>
     <t>std</t>
+  </si>
+  <si>
+    <t>AISimWithOpus47_fillna</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1282,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$B$27</c:f>
+              <c:f>Sheet2!$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1314,7 +1317,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$A$28:$A$31</c:f>
+              <c:f>Sheet2!$A$30:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1335,7 +1338,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$B$28:$B$31</c:f>
+              <c:f>Sheet2!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1360,7 +1363,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$C$27</c:f>
+              <c:f>Sheet2!$C$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1395,7 +1398,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$A$28:$A$31</c:f>
+              <c:f>Sheet2!$A$30:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1416,7 +1419,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$C$28:$C$31</c:f>
+              <c:f>Sheet2!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1761,7 +1764,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$C$27</c:f>
+              <c:f>Sheet2!$C$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1784,7 +1787,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$A$37:$A$38</c:f>
+              <c:f>Sheet2!$A$39:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1799,7 +1802,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$C$37:$C$38</c:f>
+              <c:f>Sheet2!$C$39:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1824,7 +1827,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$B$27</c:f>
+              <c:f>Sheet2!$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1847,7 +1850,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$A$35:$A$36</c:f>
+              <c:f>Sheet2!$A$37:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1862,7 +1865,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$B$35:$B$36</c:f>
+              <c:f>Sheet2!$B$37:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2271,30 +2274,33 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$A$17:$A$18</c:f>
+              <c:f>Sheet2!$A$17:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>6.2315934999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.6384999999999996</c:v>
+                  <c:v>5.1203884999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$B$17:$B$18</c:f>
+              <c:f>Sheet2!$B$17:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.22600000000000001</c:v>
+                  <c:v>-5.4421707499999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.7732499999999966E-2</c:v>
+                  <c:v>-4.4174824999999862E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2346,30 +2352,30 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$A$17:$A$18</c:f>
+              <c:f>Sheet2!$A$17:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>6.2315934999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.6384999999999996</c:v>
+                  <c:v>5.1203884999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$C$17:$C$18</c:f>
+              <c:f>Sheet2!$C$17:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
+                <c:ptCount val="3"/>
+                <c:pt idx="2">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.25373249999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4361,7 +4367,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>473261</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4397,7 +4403,7 @@
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>606612</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4465,16 +4471,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>411256</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>94727</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>601756</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>69327</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4504,7 +4510,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13290550" y="1746250"/>
+          <a:off x="15500350" y="177800"/>
           <a:ext cx="5611906" cy="1923527"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4519,13 +4525,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4567,13 +4573,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7556,12 +7562,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D15DE7-CAF9-4A3C-99EC-AE501B1448E2}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
     <col min="4" max="4" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
   </cols>
@@ -7573,6 +7579,18 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
+      <c r="H1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L1" t="s">
+        <v>321</v>
+      </c>
+      <c r="M1" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -7584,6 +7602,24 @@
       <c r="C2">
         <v>1.113</v>
       </c>
+      <c r="G2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2">
+        <v>2.7743699999999998</v>
+      </c>
+      <c r="I2">
+        <v>2.8641299999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L2">
+        <v>5.6759909999999998</v>
+      </c>
+      <c r="M2">
+        <v>0.5556025</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -7595,6 +7631,15 @@
       <c r="C3">
         <v>-0.22700000000000001</v>
       </c>
+      <c r="K3" t="s">
+        <v>320</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -7606,6 +7651,24 @@
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="G4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H4">
+        <v>0.27068130000000001</v>
+      </c>
+      <c r="I4">
+        <v>0.29724149999999999</v>
+      </c>
+      <c r="K4" t="s">
+        <v>319</v>
+      </c>
+      <c r="L4">
+        <v>0.55539000000000005</v>
+      </c>
+      <c r="M4">
+        <v>0.15205959999999999</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -7617,6 +7680,15 @@
       <c r="D5" t="s">
         <v>127</v>
       </c>
+      <c r="K5" t="s">
+        <v>320</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -7771,140 +7843,196 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>0</v>
+        <f>L2+M2</f>
+        <v>6.2315934999999998</v>
       </c>
       <c r="B17">
-        <f>B2+B3*A17</f>
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="C17">
-        <f>B3*A17</f>
-        <v>0</v>
+        <f>$B$2+$B$3*A17</f>
+        <v>-5.4421707499999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f>2.77437+2.86413</f>
-        <v>5.6384999999999996</v>
+        <f>L2-M2</f>
+        <v>5.1203884999999998</v>
       </c>
       <c r="B18">
-        <f>B2+B3*A18</f>
-        <v>-2.7732499999999966E-2</v>
-      </c>
-      <c r="C18">
-        <f>B3*A18</f>
-        <v>-0.25373249999999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>186</v>
-      </c>
-      <c r="B27" t="s">
+        <f>$B$2+$B$3*A18</f>
+        <v>-4.4174824999999862E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>316</v>
+      </c>
+      <c r="B21" t="s">
         <v>317</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C21" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f>L7+M7</f>
+        <v>6.2315934999999998</v>
+      </c>
+      <c r="B22">
+        <f>$C$2+$C$3*A22</f>
+        <v>-0.30157172450000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
         <f>L7-M7</f>
         <v>5.1203884999999998</v>
       </c>
-      <c r="B28">
-        <f>B6+B7*A28+B8*A28</f>
+      <c r="B23">
+        <f>$C$2+$C$3*A23</f>
+        <v>-4.9328189499999953E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
+        <v>317</v>
+      </c>
+      <c r="C29" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f>L7-M7</f>
+        <v>5.1203884999999998</v>
+      </c>
+      <c r="B30">
+        <f>B6+B7*A30+B8*A30</f>
         <v>0.25388736600000006</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
         <f>L7+M7</f>
         <v>6.2315934999999998</v>
       </c>
-      <c r="B29">
-        <f>B6+B7*A29+A29*B8</f>
+      <c r="B31">
+        <f>B6+B7*A31+A31*B8</f>
         <v>0.16054614600000006</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
         <f>L8-M8</f>
         <v>2.1058599999999998</v>
       </c>
-      <c r="C30">
-        <f>B7*(A30)</f>
+      <c r="C32">
+        <f>B7*(A32)</f>
         <v>-5.4752359999999993E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
         <f>L8+M8</f>
         <v>4.780926</v>
       </c>
-      <c r="C31">
-        <f>B7*A31</f>
+      <c r="C33">
+        <f>B7*A33</f>
         <v>-0.124304076</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>229</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>317</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C36" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
         <f>L9-M9</f>
         <v>0.40333040000000009</v>
       </c>
-      <c r="B35">
-        <f>D9*A35+D10*A35</f>
+      <c r="B37">
+        <f>D9*A37+D10*A37</f>
         <v>0.15528220400000003</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
         <f>L9+M9</f>
         <v>0.70744960000000001</v>
       </c>
-      <c r="B36">
-        <f>D9*A36+D10*A36</f>
+      <c r="B38">
+        <f>D9*A38+D10*A38</f>
         <v>0.272368096</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
         <f>L10-M10</f>
         <v>0.25836000000000003</v>
       </c>
-      <c r="C37">
-        <f>D9*A37</f>
+      <c r="C39">
+        <f>D9*A39</f>
         <v>0.12762984000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
         <f>L10+M10</f>
         <v>0.63216220000000001</v>
       </c>
-      <c r="C38">
-        <f>D9*A38</f>
+      <c r="C40">
+        <f>D9*A40</f>
         <v>0.31228812680000001</v>
       </c>
     </row>
